--- a/filer/81198411_hummel.xlsx
+++ b/filer/81198411_hummel.xlsx
@@ -7592,7 +7592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7697,59 +7697,24 @@
       </c>
       <c r="B4" s="37" t="inlineStr">
         <is>
-          <t>fsa:IncreaseDecreaseOfInvestmentsThroughNetExchangeDifferencesEquity</t>
+          <t>fsa:ProvisionsForInvestmentsInGroupEnterprises</t>
         </is>
       </c>
       <c r="C4" s="37" t="inlineStr">
         <is>
-          <t>fsa:IncreaseDecreaseOfInvestmentsThroughNetExchangeDifferencesEquity</t>
+          <t>fsa:ProvisionsForInvestmentsInGroupEnterprises</t>
         </is>
       </c>
       <c r="D4" s="38" t="n"/>
-      <c r="E4" s="38" t="n">
-        <v>-717</v>
-      </c>
-      <c r="F4" s="38" t="n">
-        <v>-180</v>
-      </c>
+      <c r="E4" s="38" t="n"/>
+      <c r="F4" s="38" t="n"/>
       <c r="G4" s="38" t="n">
-        <v>403</v>
+        <v>1789</v>
       </c>
       <c r="H4" s="38" t="n">
-        <v>330</v>
+        <v>423</v>
       </c>
       <c r="I4" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B5" s="34" t="inlineStr">
-        <is>
-          <t>fsa:ProvisionsForInvestmentsInGroupEnterprises</t>
-        </is>
-      </c>
-      <c r="C5" s="34" t="inlineStr">
-        <is>
-          <t>fsa:ProvisionsForInvestmentsInGroupEnterprises</t>
-        </is>
-      </c>
-      <c r="D5" s="35" t="n"/>
-      <c r="E5" s="35" t="n"/>
-      <c r="F5" s="35" t="n"/>
-      <c r="G5" s="35" t="n">
-        <v>1789</v>
-      </c>
-      <c r="H5" s="35" t="n">
-        <v>423</v>
-      </c>
-      <c r="I5" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>

--- a/filer/81198411_hummel.xlsx
+++ b/filer/81198411_hummel.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/81198411_hummel.xlsx
+++ b/filer/81198411_hummel.xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -662,7 +662,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -677,35 +677,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1531,35 +1531,35 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -3009,35 +3009,35 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
@@ -4391,19 +4391,19 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
@@ -4509,19 +4509,19 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
@@ -4819,6 +4819,13 @@
       <c r="F99" s="13">
         <f>IFERROR($F$36/($F$61+$F$68)*100,"")</f>
         <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="15" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse ikke offentliggjort (jf. koncernfritagelse, ÅRL §86, stk. 4)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4850,19 +4857,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -4872,19 +4879,19 @@
         </is>
       </c>
       <c r="B2" s="16" t="n">
-        <v>730463</v>
+        <v>1101826</v>
       </c>
       <c r="C2" s="16" t="n">
-        <v>1101826</v>
+        <v>1348615</v>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1348615</v>
+        <v>1082948</v>
       </c>
       <c r="E2" s="16" t="n">
-        <v>1082948</v>
+        <v>1219785</v>
       </c>
       <c r="F2" s="16" t="n">
-        <v>1219785</v>
+        <v>1187059</v>
       </c>
     </row>
     <row r="3">
@@ -4894,19 +4901,19 @@
         </is>
       </c>
       <c r="B3" s="16" t="n">
-        <v>2299</v>
+        <v>210</v>
       </c>
       <c r="C3" s="16" t="n">
-        <v>210</v>
+        <v>163</v>
       </c>
       <c r="D3" s="16" t="n">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>119</v>
+        <v>4155</v>
       </c>
       <c r="F3" s="16" t="n">
-        <v>4155</v>
+        <v>8492</v>
       </c>
     </row>
     <row r="4">
@@ -4916,19 +4923,19 @@
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>408872</v>
+        <v>593617</v>
       </c>
       <c r="C4" s="16" t="n">
-        <v>593617</v>
+        <v>846425</v>
       </c>
       <c r="D4" s="16" t="n">
-        <v>846425</v>
+        <v>648315</v>
       </c>
       <c r="E4" s="16" t="n">
-        <v>648315</v>
+        <v>679937</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>679937</v>
+        <v>653627</v>
       </c>
     </row>
     <row r="5">
@@ -4938,19 +4945,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>215068</v>
+        <v>314904</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>314904</v>
+        <v>451176</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>451176</v>
+        <v>385765</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>385765</v>
+        <v>389355</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>389355</v>
+        <v>344972</v>
       </c>
     </row>
     <row r="6">
@@ -4960,19 +4967,19 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>108822</v>
+        <v>193515</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>193515</v>
+        <v>51177</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>51177</v>
+        <v>48987</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>48987</v>
+        <v>154648</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>154648</v>
+        <v>196952</v>
       </c>
     </row>
     <row r="7">
@@ -4982,19 +4989,19 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>85047</v>
+        <v>109612</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>109612</v>
+        <v>147832</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>147832</v>
+        <v>152273</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>152273</v>
+        <v>167910</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>167910</v>
+        <v>219881</v>
       </c>
     </row>
     <row r="8">
@@ -5011,19 +5018,19 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>7170</v>
+        <v>8417</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>8417</v>
+        <v>11967</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>11967</v>
+        <v>12194</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>12194</v>
+        <v>10126</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>10126</v>
+        <v>24886</v>
       </c>
     </row>
     <row r="10">
@@ -5033,14 +5040,14 @@
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>1405</v>
-      </c>
-      <c r="C10" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="C10" s="16" t="n"/>
       <c r="D10" s="16" t="n"/>
       <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="F10" s="16" t="n">
+        <v>260</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
@@ -5049,19 +5056,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>15200</v>
+        <v>75486</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>75486</v>
+        <v>-108622</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>-108622</v>
+        <v>-115480</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>-115480</v>
+        <v>-23388</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>-23388</v>
+        <v>-48075</v>
       </c>
     </row>
     <row r="12">
@@ -5071,19 +5078,19 @@
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>-570</v>
+        <v>35291</v>
       </c>
       <c r="C12" s="16" t="n">
-        <v>35291</v>
+        <v>-4392</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>-4392</v>
+        <v>12563</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>12563</v>
+        <v>56828</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>56828</v>
+        <v>19546</v>
       </c>
     </row>
     <row r="13">
@@ -5093,19 +5100,19 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>5680</v>
+        <v>4585</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>4585</v>
+        <v>6652</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>6652</v>
+        <v>32856</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>32856</v>
+        <v>21749</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>21749</v>
+        <v>18800</v>
       </c>
     </row>
     <row r="14">
@@ -5114,9 +5121,7 @@
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>3849</v>
-      </c>
+      <c r="B14" s="16" t="n"/>
       <c r="C14" s="16" t="n"/>
       <c r="D14" s="16" t="n"/>
       <c r="E14" s="16" t="n"/>
@@ -5128,9 +5133,7 @@
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
-        <v>1261</v>
-      </c>
+      <c r="B15" s="16" t="n"/>
       <c r="C15" s="16" t="n"/>
       <c r="D15" s="16" t="n"/>
       <c r="E15" s="16" t="n"/>
@@ -5143,19 +5146,19 @@
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>16460</v>
+        <v>99250</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>99250</v>
+        <v>-118883</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>-118883</v>
+        <v>-115032</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>-115032</v>
+        <v>3208</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>3208</v>
+        <v>-48385</v>
       </c>
     </row>
     <row r="17">
@@ -5165,19 +5168,19 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>1029</v>
+        <v>14167</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>14167</v>
+        <v>-25093</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>-25093</v>
+        <v>-27520</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>-27520</v>
+        <v>-11791</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>-11791</v>
+        <v>-14855</v>
       </c>
     </row>
     <row r="18">
@@ -5187,19 +5190,19 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>15431</v>
+        <v>85083</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>85083</v>
+        <v>-93790</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>-93790</v>
+        <v>-87512</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>-87512</v>
+        <v>14999</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>14999</v>
+        <v>-33530</v>
       </c>
     </row>
     <row r="19">
@@ -5209,19 +5212,19 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>194</v>
+        <v>251</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>242</v>
+        <v>391</v>
       </c>
     </row>
     <row r="20">
@@ -5230,9 +5233,7 @@
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
-        <v>4985</v>
-      </c>
+      <c r="B20" s="16" t="n"/>
       <c r="C20" s="16" t="n"/>
       <c r="D20" s="16" t="n"/>
       <c r="E20" s="16" t="n"/>
@@ -5267,19 +5268,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -5289,19 +5290,19 @@
         </is>
       </c>
       <c r="B2" s="16" t="n">
-        <v>10677</v>
+        <v>11482</v>
       </c>
       <c r="C2" s="16" t="n">
-        <v>11482</v>
+        <v>15234</v>
       </c>
       <c r="D2" s="16" t="n">
-        <v>15234</v>
+        <v>8852</v>
       </c>
       <c r="E2" s="16" t="n">
-        <v>8852</v>
+        <v>3463</v>
       </c>
       <c r="F2" s="16" t="n">
-        <v>3463</v>
+        <v>5484</v>
       </c>
     </row>
     <row r="3">
@@ -5335,19 +5336,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>10677</v>
+        <v>11482</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>11482</v>
+        <v>15234</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>15234</v>
+        <v>8852</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>8852</v>
+        <v>8333</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>8333</v>
+        <v>9705</v>
       </c>
     </row>
     <row r="6">
@@ -5372,7 +5373,9 @@
       <c r="C7" s="16" t="n"/>
       <c r="D7" s="16" t="n"/>
       <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
+      <c r="F7" s="16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
@@ -5381,19 +5384,19 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>1585</v>
+        <v>3923</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>3923</v>
+        <v>6989</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>6989</v>
+        <v>4245</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>4245</v>
+        <v>3383</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>3383</v>
+        <v>92069</v>
       </c>
     </row>
     <row r="9">
@@ -5403,19 +5406,19 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>2445</v>
+        <v>2289</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>2289</v>
+        <v>1810</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>1810</v>
+        <v>919</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>919</v>
+        <v>501</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>501</v>
+        <v>5762</v>
       </c>
     </row>
     <row r="10">
@@ -5437,19 +5440,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>4030</v>
+        <v>6212</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>6212</v>
+        <v>8799</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>8799</v>
+        <v>5164</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>5164</v>
+        <v>3884</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>3884</v>
+        <v>97831</v>
       </c>
     </row>
     <row r="12">
@@ -5459,19 +5462,19 @@
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>10673</v>
+        <v>26386</v>
       </c>
       <c r="C12" s="16" t="n">
-        <v>26386</v>
+        <v>32374</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>32374</v>
+        <v>42506</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>42506</v>
+        <v>94743</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>94743</v>
+        <v>91339</v>
       </c>
     </row>
     <row r="13">
@@ -5493,19 +5496,19 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>10673</v>
+        <v>26386</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>26386</v>
+        <v>32374</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>32374</v>
+        <v>42506</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>42506</v>
+        <v>94743</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>94743</v>
+        <v>91339</v>
       </c>
     </row>
     <row r="15">
@@ -5515,19 +5518,19 @@
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>25379</v>
+        <v>44080</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>44080</v>
+        <v>56407</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>56407</v>
+        <v>56522</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>56522</v>
+        <v>106960</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>106960</v>
+        <v>198875</v>
       </c>
     </row>
     <row r="16">
@@ -5561,19 +5564,19 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>333221</v>
+        <v>441513</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>441513</v>
+        <v>719599</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>719599</v>
+        <v>495501</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>495501</v>
+        <v>525500</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>525500</v>
+        <v>434105</v>
       </c>
     </row>
     <row r="19">
@@ -5583,19 +5586,19 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>348072</v>
+        <v>452261</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>452261</v>
+        <v>719599</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>719599</v>
+        <v>497401</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>497401</v>
+        <v>525500</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>525500</v>
+        <v>434105</v>
       </c>
     </row>
     <row r="20">
@@ -5605,19 +5608,19 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>78425</v>
+        <v>108028</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>108028</v>
+        <v>113707</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>113707</v>
+        <v>72694</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>72694</v>
+        <v>57117</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>57117</v>
+        <v>67464</v>
       </c>
     </row>
     <row r="21">
@@ -5627,19 +5630,19 @@
         </is>
       </c>
       <c r="B21" s="16" t="n">
-        <v>543294</v>
+        <v>528864</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>528864</v>
+        <v>762490</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>762490</v>
+        <v>556173</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>556173</v>
+        <v>611128</v>
       </c>
       <c r="F21" s="16" t="n">
-        <v>611128</v>
+        <v>430257</v>
       </c>
     </row>
     <row r="22">
@@ -5649,19 +5652,19 @@
         </is>
       </c>
       <c r="B22" s="16" t="n">
-        <v>8990</v>
+        <v>26083</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>26083</v>
+        <v>27074</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>27074</v>
+        <v>19141</v>
       </c>
       <c r="E22" s="16" t="n">
-        <v>19141</v>
+        <v>32471</v>
       </c>
       <c r="F22" s="16" t="n">
-        <v>32471</v>
+        <v>14379</v>
       </c>
     </row>
     <row r="23">
@@ -5671,19 +5674,19 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>11087</v>
+        <v>19130</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>19130</v>
+        <v>29840</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>29840</v>
+        <v>25071</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>25071</v>
+        <v>14292</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>14292</v>
+        <v>11774</v>
       </c>
     </row>
     <row r="24">
@@ -5693,19 +5696,19 @@
         </is>
       </c>
       <c r="B24" s="16" t="n">
-        <v>5708</v>
+        <v>0</v>
       </c>
       <c r="C24" s="16" t="n">
+        <v>12924</v>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>38335</v>
+      </c>
+      <c r="E24" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="16" t="n">
-        <v>12924</v>
-      </c>
-      <c r="E24" s="16" t="n">
-        <v>38335</v>
-      </c>
       <c r="F24" s="16" t="n">
-        <v>0</v>
+        <v>9917</v>
       </c>
     </row>
     <row r="25">
@@ -5727,15 +5730,17 @@
         </is>
       </c>
       <c r="B26" s="16" t="n"/>
-      <c r="C26" s="16" t="n"/>
+      <c r="C26" s="16" t="n">
+        <v>2138</v>
+      </c>
       <c r="D26" s="16" t="n">
-        <v>2138</v>
+        <v>4062</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>4062</v>
+        <v>16551</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>16551</v>
+        <v>13440</v>
       </c>
     </row>
     <row r="27">
@@ -5745,19 +5750,19 @@
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>647504</v>
+        <v>682104</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>682104</v>
+        <v>948173</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>948173</v>
+        <v>715476</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>715476</v>
+        <v>731559</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>731559</v>
+        <v>547231</v>
       </c>
     </row>
     <row r="28">
@@ -5779,19 +5784,19 @@
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>16385</v>
+        <v>16942</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>16942</v>
+        <v>16598</v>
       </c>
       <c r="D29" s="16" t="n">
-        <v>16598</v>
+        <v>1503</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>1503</v>
+        <v>1148</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>1148</v>
+        <v>9575</v>
       </c>
     </row>
     <row r="30">
@@ -5801,19 +5806,19 @@
         </is>
       </c>
       <c r="B30" s="16" t="n">
-        <v>1011961</v>
+        <v>1151307</v>
       </c>
       <c r="C30" s="16" t="n">
-        <v>1151307</v>
+        <v>1684370</v>
       </c>
       <c r="D30" s="16" t="n">
-        <v>1684370</v>
+        <v>1214380</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>1214380</v>
+        <v>1258207</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>1258207</v>
+        <v>990911</v>
       </c>
     </row>
     <row r="31">
@@ -5823,19 +5828,19 @@
         </is>
       </c>
       <c r="B31" s="16" t="n">
-        <v>1037341</v>
+        <v>1195387</v>
       </c>
       <c r="C31" s="16" t="n">
-        <v>1195387</v>
+        <v>1740777</v>
       </c>
       <c r="D31" s="16" t="n">
-        <v>1740777</v>
+        <v>1270902</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>1270902</v>
+        <v>1365167</v>
       </c>
       <c r="F31" s="16" t="n">
-        <v>1365167</v>
+        <v>1189786</v>
       </c>
     </row>
     <row r="32">
@@ -5857,7 +5862,7 @@
         <v>10000</v>
       </c>
       <c r="F32" s="16" t="n">
-        <v>10000</v>
+        <v>10001</v>
       </c>
     </row>
     <row r="33">
@@ -5867,19 +5872,19 @@
         </is>
       </c>
       <c r="B33" s="16" t="n">
-        <v>5417</v>
+        <v>25641</v>
       </c>
       <c r="C33" s="16" t="n">
-        <v>25641</v>
+        <v>21069</v>
       </c>
       <c r="D33" s="16" t="n">
-        <v>21069</v>
+        <v>34035</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>34035</v>
+        <v>90533</v>
       </c>
       <c r="F33" s="16" t="n">
-        <v>90533</v>
+        <v>87345</v>
       </c>
     </row>
     <row r="34">
@@ -5889,19 +5894,19 @@
         </is>
       </c>
       <c r="B34" s="16" t="n">
-        <v>8328</v>
+        <v>8956</v>
       </c>
       <c r="C34" s="16" t="n">
-        <v>8956</v>
+        <v>11883</v>
       </c>
       <c r="D34" s="16" t="n">
-        <v>11883</v>
+        <v>6905</v>
       </c>
       <c r="E34" s="16" t="n">
-        <v>6905</v>
+        <v>6500</v>
       </c>
       <c r="F34" s="16" t="n">
-        <v>6500</v>
+        <v>7570</v>
       </c>
     </row>
     <row r="35">
@@ -5910,18 +5915,20 @@
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n"/>
+      <c r="B35" s="16" t="n">
+        <v>37638</v>
+      </c>
       <c r="C35" s="16" t="n">
-        <v>37638</v>
+        <v>39601</v>
       </c>
       <c r="D35" s="16" t="n">
-        <v>39601</v>
+        <v>526</v>
       </c>
       <c r="E35" s="16" t="n">
-        <v>526</v>
+        <v>16910</v>
       </c>
       <c r="F35" s="16" t="n">
-        <v>16910</v>
+        <v>-30573</v>
       </c>
     </row>
     <row r="36">
@@ -5943,19 +5950,19 @@
         </is>
       </c>
       <c r="B37" s="16" t="n">
-        <v>323799</v>
+        <v>369374</v>
       </c>
       <c r="C37" s="16" t="n">
-        <v>369374</v>
+        <v>277049</v>
       </c>
       <c r="D37" s="16" t="n">
-        <v>277049</v>
+        <v>181952</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>181952</v>
+        <v>140528</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>140528</v>
+        <v>113483</v>
       </c>
     </row>
     <row r="38">
@@ -5965,19 +5972,19 @@
         </is>
       </c>
       <c r="B38" s="16" t="n">
-        <v>322062</v>
+        <v>451609</v>
       </c>
       <c r="C38" s="16" t="n">
-        <v>451609</v>
+        <v>359602</v>
       </c>
       <c r="D38" s="16" t="n">
-        <v>359602</v>
+        <v>233418</v>
       </c>
       <c r="E38" s="16" t="n">
-        <v>233418</v>
+        <v>264471</v>
       </c>
       <c r="F38" s="16" t="n">
-        <v>264471</v>
+        <v>187826</v>
       </c>
     </row>
     <row r="39">
@@ -5987,17 +5994,17 @@
         </is>
       </c>
       <c r="B39" s="16" t="n">
+        <v>11634</v>
+      </c>
+      <c r="C39" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="C39" s="16" t="n">
-        <v>11634</v>
-      </c>
-      <c r="D39" s="16" t="n">
+      <c r="D39" s="16" t="n"/>
+      <c r="E39" s="16" t="n">
+        <v>6578</v>
+      </c>
+      <c r="F39" s="16" t="n">
         <v>0</v>
-      </c>
-      <c r="E39" s="16" t="n"/>
-      <c r="F39" s="16" t="n">
-        <v>6578</v>
       </c>
     </row>
     <row r="40">
@@ -6007,19 +6014,19 @@
         </is>
       </c>
       <c r="B40" s="16" t="n">
+        <v>11634</v>
+      </c>
+      <c r="C40" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="C40" s="16" t="n">
-        <v>11634</v>
-      </c>
       <c r="D40" s="16" t="n">
-        <v>0</v>
+        <v>1789</v>
       </c>
       <c r="E40" s="16" t="n">
-        <v>1789</v>
+        <v>7001</v>
       </c>
       <c r="F40" s="16" t="n">
-        <v>7001</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="41">
@@ -6041,7 +6048,7 @@
         </is>
       </c>
       <c r="B42" s="16" t="n">
-        <v>120000</v>
+        <v>90000</v>
       </c>
       <c r="C42" s="16" t="n">
         <v>90000</v>
@@ -6050,10 +6057,10 @@
         <v>90000</v>
       </c>
       <c r="E42" s="16" t="n">
-        <v>90000</v>
+        <v>60000</v>
       </c>
       <c r="F42" s="16" t="n">
-        <v>60000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="43">
@@ -6066,7 +6073,9 @@
       <c r="C43" s="16" t="n"/>
       <c r="D43" s="16" t="n"/>
       <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
+      <c r="F43" s="16" t="n">
+        <v>79926</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="15" t="inlineStr">
@@ -6074,18 +6083,18 @@
           <t>Anden gæld (langfristet)</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" s="16" t="n"/>
+      <c r="B44" s="16" t="n"/>
+      <c r="C44" s="16" t="n">
+        <v>50000</v>
+      </c>
       <c r="D44" s="16" t="n">
-        <v>50000</v>
+        <v>215597</v>
       </c>
       <c r="E44" s="16" t="n">
-        <v>215597</v>
+        <v>260381</v>
       </c>
       <c r="F44" s="16" t="n">
-        <v>260381</v>
+        <v>246017</v>
       </c>
     </row>
     <row r="45">
@@ -6095,19 +6104,19 @@
         </is>
       </c>
       <c r="B45" s="16" t="n">
-        <v>120000</v>
+        <v>97714</v>
       </c>
       <c r="C45" s="16" t="n">
-        <v>97714</v>
+        <v>148013</v>
       </c>
       <c r="D45" s="16" t="n">
-        <v>148013</v>
+        <v>313386</v>
       </c>
       <c r="E45" s="16" t="n">
-        <v>313386</v>
+        <v>328412</v>
       </c>
       <c r="F45" s="16" t="n">
-        <v>328412</v>
+        <v>365723</v>
       </c>
     </row>
     <row r="46">
@@ -6128,15 +6137,17 @@
           <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n"/>
+      <c r="B47" s="16" t="n">
+        <v>30000</v>
+      </c>
       <c r="C47" s="16" t="n">
         <v>30000</v>
       </c>
-      <c r="D47" s="16" t="n">
-        <v>30000</v>
-      </c>
+      <c r="D47" s="16" t="n"/>
       <c r="E47" s="16" t="n"/>
-      <c r="F47" s="16" t="n"/>
+      <c r="F47" s="16" t="n">
+        <v>10286</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="15" t="inlineStr">
@@ -6145,19 +6156,19 @@
         </is>
       </c>
       <c r="B48" s="16" t="n">
-        <v>215989</v>
+        <v>248987</v>
       </c>
       <c r="C48" s="16" t="n">
-        <v>248987</v>
+        <v>539250</v>
       </c>
       <c r="D48" s="16" t="n">
-        <v>539250</v>
+        <v>490028</v>
       </c>
       <c r="E48" s="16" t="n">
-        <v>490028</v>
+        <v>527714</v>
       </c>
       <c r="F48" s="16" t="n">
-        <v>527714</v>
+        <v>436281</v>
       </c>
     </row>
     <row r="49">
@@ -6179,19 +6190,19 @@
         </is>
       </c>
       <c r="B50" s="16" t="n">
-        <v>148435</v>
+        <v>201014</v>
       </c>
       <c r="C50" s="16" t="n">
-        <v>201014</v>
+        <v>152205</v>
       </c>
       <c r="D50" s="16" t="n">
-        <v>152205</v>
+        <v>106525</v>
       </c>
       <c r="E50" s="16" t="n">
-        <v>106525</v>
+        <v>118524</v>
       </c>
       <c r="F50" s="16" t="n">
-        <v>118524</v>
+        <v>90328</v>
       </c>
     </row>
     <row r="51">
@@ -6201,19 +6212,19 @@
         </is>
       </c>
       <c r="B51" s="16" t="n">
-        <v>167345</v>
+        <v>102574</v>
       </c>
       <c r="C51" s="16" t="n">
-        <v>102574</v>
+        <v>446719</v>
       </c>
       <c r="D51" s="16" t="n">
-        <v>446719</v>
+        <v>79324</v>
       </c>
       <c r="E51" s="16" t="n">
-        <v>79324</v>
+        <v>77141</v>
       </c>
       <c r="F51" s="16" t="n">
-        <v>77141</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="52">
@@ -6235,14 +6246,12 @@
         </is>
       </c>
       <c r="B53" s="16" t="n">
-        <v>3084</v>
+        <v>10989</v>
       </c>
       <c r="C53" s="16" t="n">
-        <v>10989</v>
-      </c>
-      <c r="D53" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="D53" s="16" t="n"/>
       <c r="E53" s="16" t="n"/>
       <c r="F53" s="16" t="n"/>
     </row>
@@ -6265,19 +6274,19 @@
         </is>
       </c>
       <c r="B55" s="16" t="n">
-        <v>60426</v>
+        <v>40867</v>
       </c>
       <c r="C55" s="16" t="n">
-        <v>40867</v>
+        <v>64988</v>
       </c>
       <c r="D55" s="16" t="n">
-        <v>64988</v>
+        <v>46432</v>
       </c>
       <c r="E55" s="16" t="n">
-        <v>46432</v>
+        <v>41904</v>
       </c>
       <c r="F55" s="16" t="n">
-        <v>41904</v>
+        <v>94808</v>
       </c>
     </row>
     <row r="56">
@@ -6299,19 +6308,19 @@
         </is>
       </c>
       <c r="B57" s="16" t="n">
-        <v>595279</v>
+        <v>634430</v>
       </c>
       <c r="C57" s="16" t="n">
-        <v>634430</v>
+        <v>1233162</v>
       </c>
       <c r="D57" s="16" t="n">
-        <v>1233162</v>
+        <v>722309</v>
       </c>
       <c r="E57" s="16" t="n">
-        <v>722309</v>
+        <v>765283</v>
       </c>
       <c r="F57" s="16" t="n">
-        <v>765283</v>
+        <v>634757</v>
       </c>
     </row>
     <row r="58">
@@ -6321,19 +6330,19 @@
         </is>
       </c>
       <c r="B58" s="16" t="n">
-        <v>715279</v>
+        <v>732145</v>
       </c>
       <c r="C58" s="16" t="n">
-        <v>732145</v>
+        <v>1381175</v>
       </c>
       <c r="D58" s="16" t="n">
-        <v>1381175</v>
+        <v>1035695</v>
       </c>
       <c r="E58" s="16" t="n">
-        <v>1035695</v>
+        <v>1093695</v>
       </c>
       <c r="F58" s="16" t="n">
-        <v>1093695</v>
+        <v>1000480</v>
       </c>
     </row>
     <row r="59">
@@ -6343,19 +6352,19 @@
         </is>
       </c>
       <c r="B59" s="16" t="n">
-        <v>1037341</v>
+        <v>1195387</v>
       </c>
       <c r="C59" s="16" t="n">
-        <v>1195387</v>
+        <v>1740777</v>
       </c>
       <c r="D59" s="16" t="n">
-        <v>1740777</v>
+        <v>1270902</v>
       </c>
       <c r="E59" s="16" t="n">
-        <v>1270902</v>
+        <v>1365167</v>
       </c>
       <c r="F59" s="16" t="n">
-        <v>1365167</v>
+        <v>1189786</v>
       </c>
     </row>
   </sheetData>
@@ -6394,13 +6403,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -7114,7 +7123,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -7232,7 +7241,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -7408,7 +7417,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B58" s="29" t="n"/>
@@ -7631,27 +7640,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2020 t.kr.</t>
+          <t>2021 t.kr.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2021 t.kr.</t>
+          <t>2022 t.kr.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2022 t.kr.</t>
+          <t>2023 t.kr.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2023 t.kr.</t>
+          <t>2024 t.kr.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2024 t.kr.</t>
+          <t>2025 t.kr.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -7676,9 +7685,7 @@
           <t>fsa:HedgeFund</t>
         </is>
       </c>
-      <c r="D3" s="35" t="n">
-        <v>-25483</v>
-      </c>
+      <c r="D3" s="35" t="n"/>
       <c r="E3" s="35" t="n"/>
       <c r="F3" s="35" t="n"/>
       <c r="G3" s="35" t="n"/>
@@ -7707,12 +7714,14 @@
       </c>
       <c r="D4" s="38" t="n"/>
       <c r="E4" s="38" t="n"/>
-      <c r="F4" s="38" t="n"/>
+      <c r="F4" s="38" t="n">
+        <v>1789</v>
+      </c>
       <c r="G4" s="38" t="n">
-        <v>1789</v>
+        <v>423</v>
       </c>
       <c r="H4" s="38" t="n">
-        <v>423</v>
+        <v>1480</v>
       </c>
       <c r="I4" s="39" t="inlineStr">
         <is>
